--- a/sheets/국악이꽃피는나무/검수/흥타령-꿈이로다 (5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/흥타령-꿈이로다 (5관).xlsx
@@ -3405,7 +3405,7 @@
       </c>
       <c r="J4" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㅎ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K4" s="25" t="inlineStr">
@@ -3428,7 +3428,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ㅎ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M6" s="28" t="inlineStr">
@@ -3566,7 +3566,7 @@
       <c r="I7" s="23"/>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K7" s="25" t="inlineStr">
@@ -3581,7 +3581,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 △</t>
         </is>
       </c>
@@ -3605,7 +3605,7 @@
       <c r="G8" s="27"/>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I8" s="26"/>
@@ -3659,7 +3659,7 @@
       <c r="H9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="I9" s="28" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I12" s="28" t="inlineStr">
@@ -3859,7 +3859,7 @@
       <c r="J12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="K12" s="28" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
@@ -3945,7 +3945,7 @@
       <c r="C14" s="27"/>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E14" s="26" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G14" s="26" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/흥타령-꿈이로다 (5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/흥타령-꿈이로다 (5관).xlsx
@@ -3260,24 +3260,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="46.51" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="69.11" customHeight="true">
+    <row r="3" ht="71.62" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="69.11" customHeight="true">
+    <row r="4" ht="71.62" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="69.11" customHeight="true">
+    <row r="5" ht="71.62" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="24" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="69.11" customHeight="true">
+    <row r="6" ht="71.62" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="69.11" customHeight="true">
+    <row r="7" ht="71.62" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="69.11" customHeight="true">
+    <row r="8" ht="71.62" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="27"/>
     </row>
-    <row r="9" ht="69.11" customHeight="true">
+    <row r="9" ht="71.62" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="69.11" customHeight="true">
+    <row r="10" ht="71.62" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="69.11" customHeight="true">
+    <row r="11" ht="71.62" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="69.11" customHeight="true">
+    <row r="12" ht="71.62" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="69.11" customHeight="true">
+    <row r="13" ht="71.62" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="69.11" customHeight="true">
+    <row r="14" ht="71.62" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3991,6 +3991,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>